--- a/artfynd/A 61166-2025 artfynd.xlsx
+++ b/artfynd/A 61166-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 61166-2025 artfynd.xlsx
+++ b/artfynd/A 61166-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129438234</v>
+        <v>102308408</v>
       </c>
       <c r="B2" t="n">
-        <v>58066</v>
+        <v>105493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103008</v>
+        <v>747</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grusnejlika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Gypsophila muralis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rosenholm, Bl</t>
+          <t>Rosenholm, vid Förrådsvägen N E22, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537987</v>
+        <v>537930</v>
       </c>
       <c r="R2" t="n">
-        <v>6229590</v>
+        <v>6229659</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -738,19 +752,24 @@
           <t>Karlskrona</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>K-Kna-1984</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ramboll naturvärdesinventering med tillägg fågelinventering</t>
+          <t>Minst 50 ex,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,43 +780,52 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grusig vägkant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eila Forsman</t>
+          <t>Åke Widgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eila Forsman, Isak Holmberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129437775</v>
+        <v>129513948</v>
       </c>
       <c r="B3" t="n">
-        <v>57866</v>
+        <v>56879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>100070</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -812,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537891</v>
+        <v>537861</v>
       </c>
       <c r="R3" t="n">
-        <v>6229721</v>
+        <v>6229778</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,17 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ramboll naturvärdesinventering med tillägg fågelinventering</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +912,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129438104</v>
+        <v>129438234</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58286</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537806</v>
+        <v>537987</v>
       </c>
       <c r="R4" t="n">
-        <v>6229714</v>
+        <v>6229590</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,32 +1014,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129513948</v>
+        <v>129438104</v>
       </c>
       <c r="B5" t="n">
-        <v>56664</v>
+        <v>58238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100070</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sandödla</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lacerta agilis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537861</v>
+        <v>537806</v>
       </c>
       <c r="R5" t="n">
-        <v>6229778</v>
+        <v>6229714</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,22 +1079,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ramboll naturvärdesinventering med tillägg fågelinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,6 +1113,218 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129437775</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rosenholm, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>537891</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6229721</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ramboll naturvärdesinventering med tillägg fågelinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eila Forsman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eila Forsman, Isak Holmberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118444670</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89079</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>239209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kantarellvaxing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hygrocybe cantharellus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rosenholm, vid Förrådsvägen, Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>537928</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6229657</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>grusvägskant med torrängsvegetation</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åke Widgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61166-2025 artfynd.xlsx
+++ b/artfynd/A 61166-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102308408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513948</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129438234</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129438104</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129437775</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,8 +1355,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118444670</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>